--- a/docs/qa/GoService_Test_Scenario_QA.xlsx
+++ b/docs/qa/GoService_Test_Scenario_QA.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C49"/>
+  <dimension ref="B2:C53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -588,7 +588,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2.0 (black-box)</t>
+          <t>2.1 (black-box)</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Onboarding, Profil, Kendaraan, Servis, Komponen, Pengingat, Backup/Restore, Pengaturan, Non-Fungsional</t>
+          <t>Onboarding, Profil, Kendaraan, Servis (Komponen/Rutin/Manual), Komponen, Pengingat (Komponen/Manual), Backup/Restore, Pengaturan (toggle + tes notif), Notifikasi (Pengingat servis &amp; Update KM), Non-Fungsional</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Kendaraan, tanggal, dan odometer wajib. Biaya minimal 0. Jika odometer servis lebih besar, odometer kendaraan ikut naik.</t>
+          <t>Servis: pilih mode Komponen / Rutin / Manual. Komponen wajib pilih dari komponen kendaraan yang dipantau. Rutin otomatis membuat pengingat berikutnya. Manual butuh judul bebas dan TIDAK membuat pengingat. Kendaraan, tanggal, dan odometer wajib. Jika odometer servis lebih besar, odometer kendaraan ikut naik.</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Kendaraan &amp; judul wajib. Pilih pemicu: berdasarkan KM, Tanggal, atau Keduanya.</t>
+          <t>Pengingat: pilih mode Komponen (auto isi judul, target km, dan tanggal dari interval komponen) atau Manual (judul bebas + pilih pemicu KM/Tanggal/Keduanya). Kendaraan wajib.</t>
         </is>
       </c>
     </row>
@@ -1033,6 +1033,54 @@
       <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Race-condition tingkat thread (selain uji tap-ganda yang terlihat di UI).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Dua saluran terpisah: 'Pengingat servis' (jatuh tempo reminder) dan 'Update KM' (otomatis 14 hari sejak update odometer terakhir, fires jam 9 pagi). Tap notif Update KM membuka layar Update KM kendaraan tersebut. Izin POST_NOTIFICATIONS diminta saat onboarding atau saat tombol tes notif ditekan; bila ditolak, app mengarahkan ke Setelan sistem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bottom-nav '+'</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tap tombol '+' di bottom-nav saat belum ada kendaraan menampilkan popup 'Tambah kendaraan dulu' dengan tombol 'Tambah Kendaraan' (lanjut) dan 'Batal'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Error form</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Setiap 'Simpan' yang gagal (validasi/penyimpanan) menampilkan Snackbar berbahasa Indonesia (mis. 'Gagal: Field nickname wajib diisi') — tidak ada tombol yang diam tanpa feedback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tips (MVP)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fitur Tips disembunyikan untuk MVP — tidak ada tile QuickAction 'Tips' di Home, dan EmptyState 'Belum ada kendaraan' tidak memiliki tombol sekunder 'Pelajari dulu'.</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4758,6 +4806,172 @@
       </c>
       <c r="L17" s="8" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>VEH-017</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Daftar Kendaraan</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Bottom-nav '+' saat garasi kosong → popup 'Tambah kendaraan dulu'</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Belum ada kendaraan.</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>1. Berada di Home empty state.
+2. Tap tombol '+' di bottom nav.</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Muncul popup 'Tambah kendaraan dulu' dengan tombol 'Tambah Kendaraan' (membuka form Tambah Kendaraan) dan 'Batal' (menutup popup). Tidak diarahkan ke Catat Servis.</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr"/>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>VEH-018</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Detail Kendaraan</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Kelola / Tambah Komponen dari Home tetap navigasi meski tanpa id eksplisit</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Fungsional</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Ada minimal 1 kendaraan.</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>1. Dari Home, tap kartu kendaraan (atau row 'Lihat detail' di hero).
+2. Tap 'Kelola' di bagian Komponen.
+3. Kembali, lalu tap '+ Tambah komponen' di grid komponen.</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>Kedua aksi navigasi ke layar yang benar (Vehicle Components untuk Kelola, Add Custom Component untuk Tambah). Tidak ada tap yang diam tanpa reaksi.</t>
+        </is>
+      </c>
+      <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>VEH-019</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Detail Kendaraan</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Bagian 'Servis terakhir' menampilkan data sebenarnya</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Fungsional</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Sudah pernah catat minimal 1 servis untuk kendaraan ini.</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka Detail Kendaraan.
+2. Gulir ke bagian 'Servis terakhir'.</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Daftar menampilkan hingga 3 servis terbaru kendaraan tersebut dengan tanggal id-ID, km berformat titik, biaya 'Rp ...'. Bila belum ada servis, tampil teks empty state mengarahkan ke tombol '+'.</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="inlineStr"/>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L17"/>
   <dataValidations count="1">
@@ -4775,7 +4989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4888,18 +5102,20 @@
       <c r="G2" s="8" t="inlineStr">
         <is>
           <t>1. Buka Catat Servis.
-2. Pilih jenis, tanggal, odometer, biaya.
-3. Simpan.</t>
+2. Pastikan mode 'Komponen' aktif.
+3. Pilih kendaraan + 1 komponen yang dipantau.
+4. Isi tanggal, odometer, biaya.
+5. Simpan.</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Ganti Oli, hari ini, 2000 km, Rp75.000</t>
+          <t>mode=Komponen, kendaraan=Vario, komponen=Oli mesin, hari ini, 2000 km, Rp75.000</t>
         </is>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>Servis tersimpan dan muncul di Riwayat.</t>
+          <t>Servis tersimpan, muncul di Riwayat. Jadwal komponen oli mesin diperbarui (badge urgensi reset).</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr"/>
@@ -5143,7 +5359,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Semua jenis servis tersedia</t>
+          <t>Mode picker tampilkan Komponen / Rutin / Manual</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -5153,7 +5369,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Sedang</t>
+          <t>Tinggi</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -5163,17 +5379,18 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1. Buka pilihan jenis servis.</t>
+          <t>1. Buka Catat Servis.
+2. Amati pilihan mode di bagian 'Jenis catatan'.</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Oli, Filter, Ban, Aki, Rem, Radiator, Tune-up, Lainnya</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>Kedelapan jenis tersedia &amp; bisa dipilih.</t>
+          <t>Terlihat 3 pilihan: Komponen (default), Rutin, Manual. Tap setiap mode mengubah konten form di bawahnya.</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr"/>
@@ -5197,7 +5414,7 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Pilih komponen terkait servis</t>
+          <t>Mode Komponen ambil daftar dari komponen yang dipantau kendaraan terpilih</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -5217,18 +5434,19 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>1. Pilih beberapa komponen.
-2. Simpan.</t>
+          <t>1. Pilih kendaraan A (punya komponen dipantau X, Y).
+2. Buka picker komponen — hanya X, Y yang tampil.
+3. Ganti ke kendaraan B (punya P, Q) — picker berisi P, Q saja.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>2 komponen</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Komponen terpilih tampil di detail servis.</t>
+          <t>Picker komponen mengikuti kendaraan terpilih; tidak ada item global yang nyasar.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
@@ -6001,6 +6219,397 @@
         </is>
       </c>
       <c r="L22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>SVC-022</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Catat Servis</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Mode Komponen tampil empty state saat belum dipantau</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Kendaraan terpilih BELUM punya komponen yang dipantau.</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka Catat Servis.
+2. Pastikan mode Komponen.
+3. Lihat area komponen.</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Muncul peringatan 'Belum ada komponen dipantau' yang menyarankan tambah komponen di Detail Kendaraan, atau pakai mode Rutin / Manual. Tombol Simpan tetap nonaktif sampai komponen dipilih.</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>SVC-023</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Catat Servis (Rutin)</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Mode Rutin: simpan tanpa pilih komponen</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Ada kendaraan terpilih.</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka Catat Servis.
+2. Ganti mode ke Rutin.
+3. Isi tanggal, odometer, biaya.
+4. Simpan.</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>mode=Rutin, hari ini, 18.000 km, Rp250.000</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Servis tersimpan dengan judul 'Servis Rutin'. Otomatis dibuat 1 pengingat baru di daftar Pengingat (target ~6 bulan / 4.000 km motor atau 10.000 km mobil di depan).</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>SVC-024</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Catat Servis (Manual)</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Mode Manual: judul bebas, tidak buat reminder</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Ada kendaraan terpilih.</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka Catat Servis.
+2. Ganti mode ke Manual.
+3. Isi judul 'Ganti spion'.
+4. Lengkapi tanggal/odometer/biaya.
+5. Simpan.</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>judul='Ganti spion', hari ini, 18.020 km, Rp120.000</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Servis tersimpan dengan judul 'Ganti spion' dan tampil di Riwayat. TIDAK ada pengingat baru yang muncul di daftar Pengingat.</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>SVC-025</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Catat Servis (Manual)</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Mode Manual wajib mengisi judul</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Mode Manual aktif.</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>1. Kosongkan field 'Apa yang diservis?'.
+2. Coba Simpan.</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>judul kosong</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Tombol Simpan tetap nonaktif sampai judul terisi.</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>SVC-026</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Catat Servis</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Ganti kendaraan: daftar komponen ter-prune</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Fungsional</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Mode Komponen, kendaraan A dengan komponen X dipilih.</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>1. Pilih komponen X dari kendaraan A.
+2. Ganti kendaraan ke B (yang punya komponen berbeda).
+3. Amati pilihan komponen.</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="8" t="inlineStr">
+        <is>
+          <t>Pilihan komponen X otomatis hilang (ter-prune) karena tidak ada di kendaraan B. Daftar picker berisi komponen B saja.</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr"/>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>SVC-027</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Catat Servis</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Gagal simpan tampil sebagai Snackbar berbahasa Indonesia</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Bisa direproduksi mis. dengan input rentang yang ditolak validasi.</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>1. Picu kondisi gagal (mis. tahun di Edit Kendaraan di luar 1950–2100, lalu Simpan).</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>Muncul Snackbar 'Gagal: …' dengan pesan ringkas dalam bahasa Indonesia, bukan tombol yang diam.</t>
+        </is>
+      </c>
+      <c r="J28" s="8" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>SVC-028</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Catat Servis</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Bottom-nav '+' saat kosong tampilkan popup, bukan masuk Catat Servis</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Belum ada kendaraan sama sekali.</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>1. Pastikan Home menampilkan empty state.
+2. Tap tombol '+' di bottom nav.</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>Muncul popup 'Tambah kendaraan dulu' dengan tombol 'Tambah Kendaraan'. Tidak masuk ke Catat Servis. Tap 'Tambah Kendaraan' membuka form Tambah Kendaraan.</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr"/>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L22"/>
@@ -6933,7 +7542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7025,7 +7634,7 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Pengingat berbasis KM</t>
+          <t>Manual: pengingat berbasis KM</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
@@ -7081,7 +7690,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Pengingat berbasis Tanggal</t>
+          <t>Manual: pengingat berbasis Tanggal</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
@@ -7137,7 +7746,7 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Pengingat berbasis Keduanya</t>
+          <t>Manual: pengingat berbasis Keduanya</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -7303,7 +7912,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Target km terisi otomatis di atas odometer</t>
+          <t>Manual: target km terisi otomatis di atas odometer kendaraan terpilih</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -7352,42 +7961,45 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Tambah Pengingat</t>
+          <t>Tambah Pengingat (Komponen)</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Judul otomatis mengikuti jenis servis</t>
+          <t>Mode Komponen otomatis isi judul + target km + tanggal dari interval komponen</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>UI/UX</t>
+          <t>Positif</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Rendah</t>
+          <t>Tinggi</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Di Tambah Pengingat, judul belum diubah manual.</t>
+          <t>Kendaraan terpilih punya komponen dipantau dengan interval km+tanggal.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>1. Ganti jenis servis.</t>
+          <t>1. Buka Tambah Pengingat.
+2. Mode Komponen.
+3. Pilih kendaraan + 1 komponen (mis. Oli mesin).
+4. Amati field Judul + Target KM + Tanggal.</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Oli → Filter</t>
+          <t>komponen Oli mesin interval 4.000 km / 6 bulan, odometer kendaraan 18.000</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Judul ikut berubah (mis. 'Ganti Oli' → 'Ganti Filter').</t>
+          <t>Judul otomatis 'Oli mesin'. Target KM otomatis = 18.000 + 4.000 = 22.000. Target Tanggal = hari ini + 6 bulan. Pemicu otomatis 'Keduanya'. Semua field masih bisa diubah pengguna.</t>
         </is>
       </c>
       <c r="J8" s="8" t="inlineStr"/>
@@ -7411,7 +8023,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Judul manual tidak ditimpa</t>
+          <t>Manual: judul yang sudah diketik tidak ditimpa</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -8056,6 +8668,281 @@
         </is>
       </c>
       <c r="L20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>RMD-020</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Tambah Pengingat</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Mode picker tampilkan Komponen / Manual</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Di form Tambah Pengingat.</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>1. Amati pilihan mode 'Jenis pengingat'.</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Terlihat 2 pilihan: Komponen (default) dan Manual. Tap mengubah isi form di bawahnya.</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>RMD-021</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Tambah Pengingat (Komponen)</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Empty state saat kendaraan belum punya komponen dipantau</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Mode Komponen, kendaraan tanpa komponen dipantau.</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka Tambah Pengingat.
+2. Pilih kendaraan yang belum punya komponen.
+3. Lihat area komponen.</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>Muncul info 'Belum ada komponen dipantau' yang mengarahkan ke Detail Kendaraan atau menyarankan mode Manual. Tombol Simpan tetap nonaktif.</t>
+        </is>
+      </c>
+      <c r="J22" s="8" t="inlineStr"/>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>RMD-022</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Tambah Pengingat (Komponen)</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Buka via TrackedComponentDetail otomatis pilih komponen tersebut</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Fungsional</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>Punya komponen dipantau.</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka Detail Komponen X.
+2. Tap 'Buat reminder dari komponen ini'.</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Form Tambah Pengingat terbuka dalam mode Komponen dengan komponen X sudah terpilih dan field-field terisi otomatis.</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr"/>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>RMD-023</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Daftar Pengingat</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Label pemicu dalam bahasa Indonesia</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Ada minimal 3 pengingat: salah satu pemicu KM, satu Tanggal, satu Keduanya.</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka daftar Pengingat.
+2. Amati teks ringkasan pemicu setiap baris.</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Tampilan id-ID dengan format: KM =&gt; 'Target 20.000 km' (separator titik). Tanggal =&gt; 'Jatuh tempo 5 Jun 2026'. Keduanya =&gt; 'Target 20.000 km · 5 Jun 2026'. Tidak ada teks Inggris seperti 'due date set'.</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>RMD-024</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Notifikasi</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Tap notif Pengingat servis buka layar Detail Reminder</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Fungsional</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Notifikasi Pengingat servis sudah aktif; ada 1 pengingat aktif yang sudah pernah memunculkan notif (atau gunakan tombol Tes notif servis di Pengaturan).</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>1. Tampilkan notif servis (atau tap 'Tes notif servis' di Pengaturan).
+2. Tap pada notifikasi.</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Aplikasi terbuka langsung ke halaman Detail Pengingat sesuai reminderId notifikasi (atau ke halaman default jika notifikasi tes tanpa id valid).</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L20"/>
@@ -8779,7 +9666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9075,6 +9962,389 @@
       </c>
       <c r="L5" s="8" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>SET-005</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Toggle 'Pengingat update KM' (default nyala)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Di Pengaturan → bagian Notifikasi.</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>1. Lihat nilai awal toggle 'Pengingat update KM'.
+2. Matikan lalu nyalakan kembali.
+3. Tutup &amp; buka aplikasi.</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Toggle baru terlihat di bawah 'Pengingat servis'. Default nyala. Nilai persist setelah restart.</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>SET-006</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Tes notif servis: izin diminta jika belum</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Positif</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Izin notifikasi belum diberikan (Android 13+) / belum ditentukan (iOS).</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka Pengaturan → tap 'Tes notif servis'.</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Muncul prompt izin notifikasi sistem. Bila diberi, notif tes muncul ~1 detik kemudian dengan judul 'Tes pengingat servis'.</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>SET-007</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Tes notif Update KM butuh setidaknya 1 kendaraan</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Belum ada kendaraan.</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>1. Tap 'Tes notif update KM' di Pengaturan.</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Tidak ada notif yang dikirim; muncul pesan singkat 'Tambah kendaraan dulu' (Toast Android / serupa iOS).</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>SET-008</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Tes notif Update KM tap → buka Update KM kendaraan</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Fungsional</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Ada minimal 1 kendaraan. Izin notifikasi diberikan.</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>1. Tap 'Tes notif update KM' di Pengaturan.
+2. Buka shade notifikasi.
+3. Tap notifikasi.</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Notif tampil di channel 'Update KM' (Android) / kategori ODOMETER_REMINDER (iOS). Tap notif membuka layar Update KM untuk kendaraan pertama.</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>SET-009</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Izin notifikasi ditolak → diarahkan ke Setelan</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Negatif</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Tinggi</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Pengguna sebelumnya menolak izin notifikasi atau memilih 'Jangan tanyakan lagi'.</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>1. Tap salah satu tombol Tes notif.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Android: muncul Toast 'Izin notifikasi ditolak. Aktifkan di Setelan...'. iOS: muncul alert 'Izin notifikasi dimatikan' dengan tombol 'Buka Setelan' yang membuka Setelan iOS. Tidak ada notif yang dikirim.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>SET-010</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Dua channel terpisah di Setelan sistem</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Salah satu notif tes pernah dikirim (Android) / kategori sudah terdaftar (iOS).</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>1. Buka Setelan sistem → Aplikasi → ServisGo → Notifikasi.</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Terlihat 2 kategori/channel: 'Pengingat servis' dan 'Update KM'. Masing-masing bisa dimatikan tanpa mempengaruhi yang lain.</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>SET-011</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Pengaturan</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Pengingat Update KM otomatis terjadwal setelah 14 hari</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Fungsional</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Sedang</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Toggle 'Pengingat update KM' nyala. Ada kendaraan yang baru saja diisi odometer-nya hari ini.</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>1. Catat update KM untuk kendaraan A hari ini.
+2. (Observasi) tunggu 14 hari, atau gunakan time-shift perangkat untuk maju 14 hari ke jam 9 pagi.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Pada jam 9 pagi hari ke-14, notif 'Update KM &lt;kendaraan A&gt;' muncul. Sebelum itu tidak ada notif update KM untuk kendaraan A.</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>Belum Diuji</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L5"/>
   <dataValidations count="1">
